--- a/小野町_引継ぎ_整理済/03_計画素案/小野町_第10期_成果指標目標値案_20260813.xlsx
+++ b/小野町_引継ぎ_整理済/03_計画素案/小野町_第10期_成果指標目標値案_20260813.xlsx
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>**在宅の認定者の4割超が未利用。**未利用理由の92.9％が需要側（状態ではない46.8％、本人の希望なし29.2％、家族が介護16.9％）で、供給制約は0.6％。したがって供給を増やしても下がらず、認定運用の確認・利用意向への働きかけ・レスパイトで下げる</t>
+          <t>**在宅の認定者の4割超が未利用。**未利用理由の上位3つは需要側（状態ではない46.8％、本人の希望なし29.2％、家族が介護16.9％）で、供給側の理由を挙げた方は1人。したがって供給を増やしても下がらず、認定運用の確認・利用意向への働きかけ・レスパイトで下げる</t>
         </is>
       </c>
       <c r="I40" s="11" t="inlineStr">

--- a/小野町_引継ぎ_整理済/03_計画素案/小野町_第10期_成果指標目標値案_20260813.xlsx
+++ b/小野町_引継ぎ_整理済/03_計画素案/小野町_第10期_成果指標目標値案_20260813.xlsx
@@ -2948,7 +2948,7 @@
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>**認定率は県内2位である一方、在宅の給付月額は県内23位。**認定を受けた方がサービスに至っていない。1.7ポイントの改善を置く</t>
+          <t>**認定率は高い一方、在宅の給付月額は県内28位／59。**認定を受けた方がサービスに至っていない。1.7ポイントの改善を置く</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
